--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/52.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/52.xlsx
@@ -426,13 +426,13 @@
         <v>-18.51800241664134</v>
       </c>
       <c r="E2">
-        <v>-28.05726321041316</v>
+        <v>-32.91975519665228</v>
       </c>
       <c r="F2">
-        <v>-3.056559063773889</v>
+        <v>-3.775159502028432</v>
       </c>
       <c r="G2">
-        <v>-18.41741679583754</v>
+        <v>-22.53066203565196</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.16632728562569</v>
       </c>
       <c r="E3">
-        <v>-26.78799987317328</v>
+        <v>-33.54828248230989</v>
       </c>
       <c r="F3">
-        <v>-3.006595255506634</v>
+        <v>-3.63682380249572</v>
       </c>
       <c r="G3">
-        <v>-18.7752735264506</v>
+        <v>-22.35015950594151</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.78252261837654</v>
       </c>
       <c r="E4">
-        <v>-29.48139130176736</v>
+        <v>-33.0337685867434</v>
       </c>
       <c r="F4">
-        <v>-3.564295266176206</v>
+        <v>-3.563826410226222</v>
       </c>
       <c r="G4">
-        <v>-18.97453857300487</v>
+        <v>-21.88556416605127</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.38453171877457</v>
       </c>
       <c r="E5">
-        <v>-30.91738852349566</v>
+        <v>-34.76770543462136</v>
       </c>
       <c r="F5">
-        <v>-2.981345788701902</v>
+        <v>-3.496220033014143</v>
       </c>
       <c r="G5">
-        <v>-18.36532370650434</v>
+        <v>-21.71470360022395</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.99265881901083</v>
       </c>
       <c r="E6">
-        <v>-29.15432679503738</v>
+        <v>-34.25764982171542</v>
       </c>
       <c r="F6">
-        <v>-2.497545262403476</v>
+        <v>-3.471496579510189</v>
       </c>
       <c r="G6">
-        <v>-18.39811797061636</v>
+        <v>-21.59241204800327</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.62590644937255</v>
       </c>
       <c r="E7">
-        <v>-30.95592130882693</v>
+        <v>-34.41678266258196</v>
       </c>
       <c r="F7">
-        <v>-2.419493172242095</v>
+        <v>-3.390389470367284</v>
       </c>
       <c r="G7">
-        <v>-18.3487047678972</v>
+        <v>-20.90514610459611</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.28765442151332</v>
       </c>
       <c r="E8">
-        <v>-30.79180714655195</v>
+        <v>-35.57052009941216</v>
       </c>
       <c r="F8">
-        <v>-2.20410770710539</v>
+        <v>-3.373440244938603</v>
       </c>
       <c r="G8">
-        <v>-17.43330913137886</v>
+        <v>-20.60189020156225</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-15.97881509458637</v>
       </c>
       <c r="E9">
-        <v>-31.13865882045845</v>
+        <v>-35.14887162032097</v>
       </c>
       <c r="F9">
-        <v>-2.382478403215402</v>
+        <v>-3.364576713728649</v>
       </c>
       <c r="G9">
-        <v>-17.60182417569161</v>
+        <v>-20.7415240465904</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.73080999628841</v>
       </c>
       <c r="E10">
-        <v>-30.54805976885209</v>
+        <v>-35.97486980779406</v>
       </c>
       <c r="F10">
-        <v>-2.416785239202344</v>
+        <v>-3.359365454397637</v>
       </c>
       <c r="G10">
-        <v>-17.9520418224728</v>
+        <v>-20.27229559821795</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.55995281654188</v>
       </c>
       <c r="E11">
-        <v>-32.41610058175619</v>
+        <v>-36.69799238699789</v>
       </c>
       <c r="F11">
-        <v>-2.285055769706958</v>
+        <v>-3.16534938315095</v>
       </c>
       <c r="G11">
-        <v>-18.20538628568384</v>
+        <v>-19.37435646832819</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.46957060434808</v>
       </c>
       <c r="E12">
-        <v>-33.5014127763305</v>
+        <v>-36.89390775799173</v>
       </c>
       <c r="F12">
-        <v>-2.190827320903709</v>
+        <v>-3.242203654047883</v>
       </c>
       <c r="G12">
-        <v>-16.7180939072564</v>
+        <v>-19.51402838463004</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.45842419815894</v>
       </c>
       <c r="E13">
-        <v>-33.42239543337066</v>
+        <v>-37.11007220051087</v>
       </c>
       <c r="F13">
-        <v>-1.614320885088379</v>
+        <v>-2.899086420501703</v>
       </c>
       <c r="G13">
-        <v>-16.82459084670922</v>
+        <v>-19.24262986132059</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.55234320299835</v>
       </c>
       <c r="E14">
-        <v>-34.92788208874666</v>
+        <v>-37.3062162594421</v>
       </c>
       <c r="F14">
-        <v>-1.77096350422296</v>
+        <v>-3.026412288883806</v>
       </c>
       <c r="G14">
-        <v>-16.46505566950775</v>
+        <v>-18.79979804780552</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.75056896809381</v>
       </c>
       <c r="E15">
-        <v>-34.90701940899333</v>
+        <v>-38.08065550610085</v>
       </c>
       <c r="F15">
-        <v>-2.123671575558753</v>
+        <v>-2.680812438231436</v>
       </c>
       <c r="G15">
-        <v>-15.31462288661055</v>
+        <v>-18.40306227037926</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-16.03194510061648</v>
       </c>
       <c r="E16">
-        <v>-34.11594028459339</v>
+        <v>-38.612683274892</v>
       </c>
       <c r="F16">
-        <v>-1.106380904304972</v>
+        <v>-2.599781538889588</v>
       </c>
       <c r="G16">
-        <v>-15.13823867555095</v>
+        <v>-18.54294937214117</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-16.37357817653108</v>
       </c>
       <c r="E17">
-        <v>-34.93246490444243</v>
+        <v>-38.60216136553518</v>
       </c>
       <c r="F17">
-        <v>-2.105956110282483</v>
+        <v>-2.365467050231512</v>
       </c>
       <c r="G17">
-        <v>-14.58238649259793</v>
+        <v>-18.13809613705261</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-16.76428833448615</v>
       </c>
       <c r="E18">
-        <v>-38.73855900264621</v>
+        <v>-39.32489223173734</v>
       </c>
       <c r="F18">
-        <v>-1.172357054468342</v>
+        <v>-2.305196694738625</v>
       </c>
       <c r="G18">
-        <v>-14.43063605089605</v>
+        <v>-18.08330329783213</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-17.1698376222828</v>
       </c>
       <c r="E19">
-        <v>-37.39305880548719</v>
+        <v>-40.0438984280682</v>
       </c>
       <c r="F19">
-        <v>-1.414809424491521</v>
+        <v>-2.218370537046792</v>
       </c>
       <c r="G19">
-        <v>-14.03165406832139</v>
+        <v>-17.93640115007252</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-17.5398035034324</v>
       </c>
       <c r="E20">
-        <v>-36.51531148129146</v>
+        <v>-40.57779192815052</v>
       </c>
       <c r="F20">
-        <v>-0.5459621918194115</v>
+        <v>-1.879294908058871</v>
       </c>
       <c r="G20">
-        <v>-13.6944054836903</v>
+        <v>-17.93697221917804</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-17.83969777356175</v>
       </c>
       <c r="E21">
-        <v>-38.45913857095093</v>
+        <v>-40.57640395086717</v>
       </c>
       <c r="F21">
-        <v>-1.010253009047104</v>
+        <v>-1.788113194563118</v>
       </c>
       <c r="G21">
-        <v>-14.49638017476043</v>
+        <v>-17.83908104285456</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-18.05044958230462</v>
       </c>
       <c r="E22">
-        <v>-40.38172032480341</v>
+        <v>-41.84711866402651</v>
       </c>
       <c r="F22">
-        <v>-1.396648297552544</v>
+        <v>-1.930848353372098</v>
       </c>
       <c r="G22">
-        <v>-13.62824423108796</v>
+        <v>-17.87856591950145</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-18.1484671636742</v>
       </c>
       <c r="E23">
-        <v>-39.33674098397842</v>
+        <v>-41.98585072948849</v>
       </c>
       <c r="F23">
-        <v>-1.499475199996853</v>
+        <v>-1.957529239048867</v>
       </c>
       <c r="G23">
-        <v>-14.19876378605272</v>
+        <v>-17.6554715661555</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-18.10609501245165</v>
       </c>
       <c r="E24">
-        <v>-39.92179265492538</v>
+        <v>-41.433546718328</v>
       </c>
       <c r="F24">
-        <v>-1.016642206824896</v>
+        <v>-1.68397250141797</v>
       </c>
       <c r="G24">
-        <v>-14.00218193665803</v>
+        <v>-17.49816768431149</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-17.92630379552337</v>
       </c>
       <c r="E25">
-        <v>-39.82696867344177</v>
+        <v>-41.84213281414407</v>
       </c>
       <c r="F25">
-        <v>-0.5202471825343065</v>
+        <v>-1.83263462899398</v>
       </c>
       <c r="G25">
-        <v>-13.97784115058054</v>
+        <v>-17.11563083670317</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-17.62556976315426</v>
       </c>
       <c r="E26">
-        <v>-39.30593377530423</v>
+        <v>-42.16070643210966</v>
       </c>
       <c r="F26">
-        <v>-0.7791012271329155</v>
+        <v>-1.802367740830492</v>
       </c>
       <c r="G26">
-        <v>-12.09520838967165</v>
+        <v>-17.57309360622905</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-17.22017746140667</v>
       </c>
       <c r="E27">
-        <v>-38.77127269887762</v>
+        <v>-42.44583726952862</v>
       </c>
       <c r="F27">
-        <v>-2.184766984984827</v>
+        <v>-1.789138713407784</v>
       </c>
       <c r="G27">
-        <v>-12.40787617367365</v>
+        <v>-17.27040215120963</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-16.72016646822192</v>
       </c>
       <c r="E28">
-        <v>-39.4055103902589</v>
+        <v>-42.19651534032532</v>
       </c>
       <c r="F28">
-        <v>-1.665835397133674</v>
+        <v>-1.787951662919572</v>
       </c>
       <c r="G28">
-        <v>-12.27856295436418</v>
+        <v>-17.27219977743746</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-16.16707085170393</v>
       </c>
       <c r="E29">
-        <v>-38.82031154390668</v>
+        <v>-41.98357290706264</v>
       </c>
       <c r="F29">
-        <v>-0.9037804616630748</v>
+        <v>-2.009525032555189</v>
       </c>
       <c r="G29">
-        <v>-13.22148577704156</v>
+        <v>-17.45729734435642</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-15.60418040230303</v>
       </c>
       <c r="E30">
-        <v>-37.87796100951753</v>
+        <v>-41.4132976468027</v>
       </c>
       <c r="F30">
-        <v>-1.39587460239833</v>
+        <v>-2.008026515923525</v>
       </c>
       <c r="G30">
-        <v>-12.75670835714666</v>
+        <v>-17.26217379027177</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-15.06473316530547</v>
       </c>
       <c r="E31">
-        <v>-37.8037347920578</v>
+        <v>-42.01149774203093</v>
       </c>
       <c r="F31">
-        <v>-0.6943468163154841</v>
+        <v>-1.880400778541608</v>
       </c>
       <c r="G31">
-        <v>-12.19556095660358</v>
+        <v>-17.22419521184526</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-14.56451028393051</v>
       </c>
       <c r="E32">
-        <v>-38.38930723751564</v>
+        <v>-41.57191877010637</v>
       </c>
       <c r="F32">
-        <v>-0.09810784059806719</v>
+        <v>-1.822376127077711</v>
       </c>
       <c r="G32">
-        <v>-13.63797061388234</v>
+        <v>-17.60442295393994</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-14.14021143740034</v>
       </c>
       <c r="E33">
-        <v>-40.33760845949469</v>
+        <v>-41.32194700488297</v>
       </c>
       <c r="F33">
-        <v>-1.450659508949877</v>
+        <v>-1.64742327487165</v>
       </c>
       <c r="G33">
-        <v>-13.46899871428517</v>
+        <v>-17.80378235104208</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-13.81338390512137</v>
       </c>
       <c r="E34">
-        <v>-37.60360114752581</v>
+        <v>-40.81465828959572</v>
       </c>
       <c r="F34">
-        <v>-1.275749731848762</v>
+        <v>-1.911123268776636</v>
       </c>
       <c r="G34">
-        <v>-13.81343118273648</v>
+        <v>-17.21389941521812</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-13.58657698804389</v>
       </c>
       <c r="E35">
-        <v>-35.89452788618697</v>
+        <v>-40.66347065637564</v>
       </c>
       <c r="F35">
-        <v>-0.5602540146199114</v>
+        <v>-1.994650867470521</v>
       </c>
       <c r="G35">
-        <v>-13.0973999091386</v>
+        <v>-17.72605901814384</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-13.44235509918192</v>
       </c>
       <c r="E36">
-        <v>-35.77360857323416</v>
+        <v>-40.30441021654446</v>
       </c>
       <c r="F36">
-        <v>-1.385334455565109</v>
+        <v>-2.119786532439623</v>
       </c>
       <c r="G36">
-        <v>-13.17389999546007</v>
+        <v>-17.74459310734545</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-13.38499556370472</v>
       </c>
       <c r="E37">
-        <v>-36.4568285037194</v>
+        <v>-40.10457092282297</v>
       </c>
       <c r="F37">
-        <v>-1.22892626440552</v>
+        <v>-2.200080184792979</v>
       </c>
       <c r="G37">
-        <v>-13.8565940754775</v>
+        <v>-17.58344899267589</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-13.40268315435412</v>
       </c>
       <c r="E38">
-        <v>-37.38228556582295</v>
+        <v>-39.78743962382881</v>
       </c>
       <c r="F38">
-        <v>-0.9704648659558378</v>
+        <v>-1.988116705397239</v>
       </c>
       <c r="G38">
-        <v>-14.28509784789861</v>
+        <v>-18.14817840349246</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-13.47099738780553</v>
       </c>
       <c r="E39">
-        <v>-34.37533580422676</v>
+        <v>-39.39224875412744</v>
       </c>
       <c r="F39">
-        <v>-1.308925846330882</v>
+        <v>-1.895104299941299</v>
       </c>
       <c r="G39">
-        <v>-13.17071856119684</v>
+        <v>-17.81739034848125</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-13.55645077656272</v>
       </c>
       <c r="E40">
-        <v>-36.28023386707928</v>
+        <v>-39.26536317666952</v>
       </c>
       <c r="F40">
-        <v>-1.241553068726393</v>
+        <v>-1.827203023933824</v>
       </c>
       <c r="G40">
-        <v>-14.98909694373401</v>
+        <v>-17.45490216465876</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-13.65334375199609</v>
       </c>
       <c r="E41">
-        <v>-35.08329705245291</v>
+        <v>-39.26587489423238</v>
       </c>
       <c r="F41">
-        <v>-1.061185178808231</v>
+        <v>-1.761247582955524</v>
       </c>
       <c r="G41">
-        <v>-14.52718811154889</v>
+        <v>-17.93393975946407</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-13.74534980477167</v>
       </c>
       <c r="E42">
-        <v>-36.03800126393499</v>
+        <v>-38.89050289102558</v>
       </c>
       <c r="F42">
-        <v>-1.136463066537636</v>
+        <v>-1.838218653656251</v>
       </c>
       <c r="G42">
-        <v>-13.65753262747389</v>
+        <v>-17.6319766244633</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-13.81184756618211</v>
       </c>
       <c r="E43">
-        <v>-35.09411557685723</v>
+        <v>-38.62027299732885</v>
       </c>
       <c r="F43">
-        <v>-0.912142002226933</v>
+        <v>-1.796888918828376</v>
       </c>
       <c r="G43">
-        <v>-14.62044617939016</v>
+        <v>-17.55702256290866</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-13.83298605663724</v>
       </c>
       <c r="E44">
-        <v>-34.11782865825459</v>
+        <v>-38.27565838958215</v>
       </c>
       <c r="F44">
-        <v>-0.3455444972838908</v>
+        <v>-2.035359326746297</v>
       </c>
       <c r="G44">
-        <v>-14.52366900164064</v>
+        <v>-18.15685203280535</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-13.81816857107822</v>
       </c>
       <c r="E45">
-        <v>-33.46534800933341</v>
+        <v>-37.17177039462837</v>
       </c>
       <c r="F45">
-        <v>-0.4218280230402944</v>
+        <v>-1.824436276808473</v>
       </c>
       <c r="G45">
-        <v>-14.01126110779948</v>
+        <v>-17.98570344951611</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-13.76785359649319</v>
       </c>
       <c r="E46">
-        <v>-33.28964774630981</v>
+        <v>-36.7024302915254</v>
       </c>
       <c r="F46">
-        <v>-0.4813810123623565</v>
+        <v>-1.921419047226031</v>
       </c>
       <c r="G46">
-        <v>-16.50970665246867</v>
+        <v>-17.93290521398304</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-13.67826176473284</v>
       </c>
       <c r="E47">
-        <v>-31.20280918325111</v>
+        <v>-35.92598719511826</v>
       </c>
       <c r="F47">
-        <v>-0.3649531455314831</v>
+        <v>-1.691212432518437</v>
       </c>
       <c r="G47">
-        <v>-14.45823275851141</v>
+        <v>-17.84123455272785</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-13.54895991285007</v>
       </c>
       <c r="E48">
-        <v>-32.02431286027158</v>
+        <v>-36.76267258124944</v>
       </c>
       <c r="F48">
-        <v>-0.3284130310265941</v>
+        <v>-1.891421378468453</v>
       </c>
       <c r="G48">
-        <v>-12.95562910696485</v>
+        <v>-18.09489020721958</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-13.40195026372837</v>
       </c>
       <c r="E49">
-        <v>-31.59472823048194</v>
+        <v>-35.93301991525217</v>
       </c>
       <c r="F49">
-        <v>-0.0914096617790304</v>
+        <v>-1.88265310950982</v>
       </c>
       <c r="G49">
-        <v>-15.2839341294615</v>
+        <v>-17.6209376103626</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-13.24654778659167</v>
       </c>
       <c r="E50">
-        <v>-30.7086485141121</v>
+        <v>-36.05899074096054</v>
       </c>
       <c r="F50">
-        <v>-0.8164895898582712</v>
+        <v>-1.908469179618066</v>
       </c>
       <c r="G50">
-        <v>-15.01671848044092</v>
+        <v>-17.73230436230368</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-13.08262998322567</v>
       </c>
       <c r="E51">
-        <v>-31.72738534806264</v>
+        <v>-35.07402953039621</v>
       </c>
       <c r="F51">
-        <v>-0.4034879687423134</v>
+        <v>-1.723411901832657</v>
       </c>
       <c r="G51">
-        <v>-16.09525945640731</v>
+        <v>-18.7547547651982</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-12.9158263867534</v>
       </c>
       <c r="E52">
-        <v>-30.53861337207209</v>
+        <v>-34.90756282587424</v>
       </c>
       <c r="F52">
-        <v>-0.4523508767312478</v>
+        <v>-1.793916736587131</v>
       </c>
       <c r="G52">
-        <v>-15.49563524033405</v>
+        <v>-18.26744908290856</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-12.76457953009731</v>
       </c>
       <c r="E53">
-        <v>-30.43593928089618</v>
+        <v>-34.85058103743573</v>
       </c>
       <c r="F53">
-        <v>0.146227408531675</v>
+        <v>-1.850869480631806</v>
       </c>
       <c r="G53">
-        <v>-15.84725324787835</v>
+        <v>-18.13562647008031</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-12.63399690434323</v>
       </c>
       <c r="E54">
-        <v>-31.33049177213438</v>
+        <v>-34.34503578464143</v>
       </c>
       <c r="F54">
-        <v>-0.5381158957800946</v>
+        <v>-1.892155311987333</v>
       </c>
       <c r="G54">
-        <v>-15.49980487244076</v>
+        <v>-18.04549355722812</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.51640330373959</v>
       </c>
       <c r="E55">
-        <v>-29.54597639806476</v>
+        <v>-34.58812200513618</v>
       </c>
       <c r="F55">
-        <v>-0.07484811229485988</v>
+        <v>-1.746563114006097</v>
       </c>
       <c r="G55">
-        <v>-14.38214980092788</v>
+        <v>-17.92450139413161</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.41584186128244</v>
       </c>
       <c r="E56">
-        <v>-28.70839437408005</v>
+        <v>-34.22684714151524</v>
       </c>
       <c r="F56">
-        <v>-0.3217405315970441</v>
+        <v>-1.730874663764478</v>
       </c>
       <c r="G56">
-        <v>-16.08162497460382</v>
+        <v>-18.39397978869227</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.3427689591881</v>
       </c>
       <c r="E57">
-        <v>-28.38054191287274</v>
+        <v>-33.4664642781763</v>
       </c>
       <c r="F57">
-        <v>-0.4768357604231956</v>
+        <v>-1.898409485878469</v>
       </c>
       <c r="G57">
-        <v>-15.92123400904444</v>
+        <v>-18.34081077205881</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.29643750322899</v>
       </c>
       <c r="E58">
-        <v>-28.70238961754588</v>
+        <v>-33.58412308984359</v>
       </c>
       <c r="F58">
-        <v>-1.150044978473937</v>
+        <v>-2.02619924000614</v>
       </c>
       <c r="G58">
-        <v>-15.23412200600486</v>
+        <v>-18.20468279475674</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.26227837635005</v>
       </c>
       <c r="E59">
-        <v>-26.49960400599479</v>
+        <v>-33.46954590473852</v>
       </c>
       <c r="F59">
-        <v>-0.1621754322653866</v>
+        <v>-1.922474387297198</v>
       </c>
       <c r="G59">
-        <v>-15.61896464858129</v>
+        <v>-18.64436131364566</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.24526028739595</v>
       </c>
       <c r="E60">
-        <v>-28.81756229698296</v>
+        <v>-32.76449646529931</v>
       </c>
       <c r="F60">
-        <v>-0.2050045120923294</v>
+        <v>-2.003384344998237</v>
       </c>
       <c r="G60">
-        <v>-14.66013962040602</v>
+        <v>-18.32846740301563</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-12.25039334185312</v>
       </c>
       <c r="E61">
-        <v>-27.31256471679979</v>
+        <v>-33.36760316211485</v>
       </c>
       <c r="F61">
-        <v>-0.2043095118413806</v>
+        <v>-1.819447019941412</v>
       </c>
       <c r="G61">
-        <v>-15.53484368642841</v>
+        <v>-18.05680569133581</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-12.27376189048188</v>
       </c>
       <c r="E62">
-        <v>-28.01065615592622</v>
+        <v>-32.94143753020101</v>
       </c>
       <c r="F62">
-        <v>-0.5564634053847008</v>
+        <v>-1.89900756714329</v>
       </c>
       <c r="G62">
-        <v>-14.77525225462479</v>
+        <v>-18.61985996610951</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-12.29897343164411</v>
       </c>
       <c r="E63">
-        <v>-27.06219897433772</v>
+        <v>-32.81176694122837</v>
       </c>
       <c r="F63">
-        <v>-0.7264369411325342</v>
+        <v>-2.121572492560059</v>
       </c>
       <c r="G63">
-        <v>-15.13933446612445</v>
+        <v>-18.06014603178493</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-12.33175816008316</v>
       </c>
       <c r="E64">
-        <v>-27.91273696245836</v>
+        <v>-33.20475697256202</v>
       </c>
       <c r="F64">
-        <v>-0.1792729354591684</v>
+        <v>-2.16982489377313</v>
       </c>
       <c r="G64">
-        <v>-16.05219753530524</v>
+        <v>-18.47350074781833</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-12.37363640417099</v>
       </c>
       <c r="E65">
-        <v>-26.07170849701002</v>
+        <v>-32.7777762153268</v>
       </c>
       <c r="F65">
-        <v>-0.7096119708142734</v>
+        <v>-2.148170541496548</v>
       </c>
       <c r="G65">
-        <v>-15.81300399900182</v>
+        <v>-18.51783391840748</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-12.41848841349729</v>
       </c>
       <c r="E66">
-        <v>-28.69438780397433</v>
+        <v>-32.8390011839105</v>
       </c>
       <c r="F66">
-        <v>-0.8291420735686309</v>
+        <v>-2.119193421379219</v>
       </c>
       <c r="G66">
-        <v>-16.39472312952594</v>
+        <v>-18.11467899318058</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-12.44988620407145</v>
       </c>
       <c r="E67">
-        <v>-27.9147023201777</v>
+        <v>-32.92316740181706</v>
       </c>
       <c r="F67">
-        <v>-0.7934800285107094</v>
+        <v>-2.079055707243971</v>
       </c>
       <c r="G67">
-        <v>-15.64660273801589</v>
+        <v>-18.35471837386928</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-12.47381398181855</v>
       </c>
       <c r="E68">
-        <v>-27.17228164899018</v>
+        <v>-32.59513153741243</v>
       </c>
       <c r="F68">
-        <v>-0.4431841630518685</v>
+        <v>-2.38671798758293</v>
       </c>
       <c r="G68">
-        <v>-15.25569186546598</v>
+        <v>-19.12545972304916</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-12.49003736649249</v>
       </c>
       <c r="E69">
-        <v>-27.7397130275733</v>
+        <v>-32.67867056166894</v>
       </c>
       <c r="F69">
-        <v>-1.230934226989906</v>
+        <v>-2.135586812280621</v>
       </c>
       <c r="G69">
-        <v>-15.08358653451589</v>
+        <v>-18.44711901041588</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.49162470282786</v>
       </c>
       <c r="E70">
-        <v>-27.80069798703459</v>
+        <v>-32.19871345125498</v>
       </c>
       <c r="F70">
-        <v>-0.9147712403634186</v>
+        <v>-2.068229773656785</v>
       </c>
       <c r="G70">
-        <v>-15.16978982981297</v>
+        <v>-18.05133335955939</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.46475552819035</v>
       </c>
       <c r="E71">
-        <v>-26.73570958380671</v>
+        <v>-32.28907235736703</v>
       </c>
       <c r="F71">
-        <v>-1.166942016756241</v>
+        <v>-2.130222304980091</v>
       </c>
       <c r="G71">
-        <v>-14.75455637918603</v>
+        <v>-18.08835187977952</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.41779852057724</v>
       </c>
       <c r="E72">
-        <v>-29.16708803479099</v>
+        <v>-31.99959192066371</v>
       </c>
       <c r="F72">
-        <v>-1.226817240997992</v>
+        <v>-2.240571611809222</v>
       </c>
       <c r="G72">
-        <v>-15.85192608290703</v>
+        <v>-18.38331486623751</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.35137299088766</v>
       </c>
       <c r="E73">
-        <v>-27.94527404820348</v>
+        <v>-32.75116690205773</v>
       </c>
       <c r="F73">
-        <v>-1.04350201986067</v>
+        <v>-2.395243544892542</v>
       </c>
       <c r="G73">
-        <v>-13.77571579268034</v>
+        <v>-18.68881366387422</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-12.26021444626723</v>
       </c>
       <c r="E74">
-        <v>-27.21179711318111</v>
+        <v>-32.3005090184734</v>
       </c>
       <c r="F74">
-        <v>-0.6974167459102592</v>
+        <v>-2.4067412844434</v>
       </c>
       <c r="G74">
-        <v>-14.4861770734084</v>
+        <v>-18.26734976654238</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-12.13479047897427</v>
       </c>
       <c r="E75">
-        <v>-26.33602646788972</v>
+        <v>-32.44428806821693</v>
       </c>
       <c r="F75">
-        <v>-1.557735107803145</v>
+        <v>-2.368847617602337</v>
       </c>
       <c r="G75">
-        <v>-15.26924523890376</v>
+        <v>-18.31783558601626</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.98722002433299</v>
       </c>
       <c r="E76">
-        <v>-27.98293736652527</v>
+        <v>-33.14307462810354</v>
       </c>
       <c r="F76">
-        <v>-1.292108331319247</v>
+        <v>-2.597759494059355</v>
       </c>
       <c r="G76">
-        <v>-13.8538413568616</v>
+        <v>-17.94264649423235</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.81981880153937</v>
       </c>
       <c r="E77">
-        <v>-27.29015782740984</v>
+        <v>-33.50739036202062</v>
       </c>
       <c r="F77">
-        <v>-0.9302161505886154</v>
+        <v>-2.520279805773308</v>
       </c>
       <c r="G77">
-        <v>-13.46265239848639</v>
+        <v>-17.74546378082228</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.6295958878331</v>
       </c>
       <c r="E78">
-        <v>-28.56428927420797</v>
+        <v>-33.18042548171881</v>
       </c>
       <c r="F78">
-        <v>-1.429107874231243</v>
+        <v>-2.703329120974332</v>
       </c>
       <c r="G78">
-        <v>-14.55376186059262</v>
+        <v>-17.8377435824567</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.41135221130566</v>
       </c>
       <c r="E79">
-        <v>-28.80946538545725</v>
+        <v>-33.75655605887066</v>
       </c>
       <c r="F79">
-        <v>-1.635932162260015</v>
+        <v>-2.607028096929278</v>
       </c>
       <c r="G79">
-        <v>-14.124392380513</v>
+        <v>-17.75579102763204</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.18079580512655</v>
       </c>
       <c r="E80">
-        <v>-28.65288886816804</v>
+        <v>-33.97935924428505</v>
       </c>
       <c r="F80">
-        <v>-1.546138792531354</v>
+        <v>-2.639241648489346</v>
       </c>
       <c r="G80">
-        <v>-12.38961520447903</v>
+        <v>-17.62899878875072</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.94204797459218</v>
       </c>
       <c r="E81">
-        <v>-30.40859635483787</v>
+        <v>-33.77995468406829</v>
       </c>
       <c r="F81">
-        <v>-1.141033169498881</v>
+        <v>-2.677561924542851</v>
       </c>
       <c r="G81">
-        <v>-12.57646901580658</v>
+        <v>-17.70559322562007</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.69356378927484</v>
       </c>
       <c r="E82">
-        <v>-30.84497595987601</v>
+        <v>-34.38984956342134</v>
       </c>
       <c r="F82">
-        <v>-1.684282310826617</v>
+        <v>-2.879618129801109</v>
       </c>
       <c r="G82">
-        <v>-13.53509044543118</v>
+        <v>-17.52043110306309</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.43538123010175</v>
       </c>
       <c r="E83">
-        <v>-31.98188332305671</v>
+        <v>-34.70444718120821</v>
       </c>
       <c r="F83">
-        <v>-1.059275791944778</v>
+        <v>-2.822758991272951</v>
       </c>
       <c r="G83">
-        <v>-14.61548036108125</v>
+        <v>-17.68852736336513</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.18434525797441</v>
       </c>
       <c r="E84">
-        <v>-31.21204047751575</v>
+        <v>-35.47565536166248</v>
       </c>
       <c r="F84">
-        <v>-1.858718261773331</v>
+        <v>-2.990770953010955</v>
       </c>
       <c r="G84">
-        <v>-13.03573437737859</v>
+        <v>-17.18701778543924</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.946095609379318</v>
       </c>
       <c r="E85">
-        <v>-30.67927230322434</v>
+        <v>-35.77642754830394</v>
       </c>
       <c r="F85">
-        <v>-2.091684996667053</v>
+        <v>-2.96860963988386</v>
       </c>
       <c r="G85">
-        <v>-12.56660690064509</v>
+        <v>-17.41579469020335</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.719230492359214</v>
       </c>
       <c r="E86">
-        <v>-32.72015138357919</v>
+        <v>-36.61140343549722</v>
       </c>
       <c r="F86">
-        <v>-1.918528044990261</v>
+        <v>-2.965269662515772</v>
       </c>
       <c r="G86">
-        <v>-13.38796980166597</v>
+        <v>-17.31661405639232</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.509487221163456</v>
       </c>
       <c r="E87">
-        <v>-34.27561427810384</v>
+        <v>-37.09088732037738</v>
       </c>
       <c r="F87">
-        <v>-1.896349336147707</v>
+        <v>-3.083378286806925</v>
       </c>
       <c r="G87">
-        <v>-11.60250320760746</v>
+        <v>-17.36875845918138</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.333534732737949</v>
       </c>
       <c r="E88">
-        <v>-34.78232334871812</v>
+        <v>-38.12113327101841</v>
       </c>
       <c r="F88">
-        <v>-2.846429589807947</v>
+        <v>-3.349137602075271</v>
       </c>
       <c r="G88">
-        <v>-12.21449727708821</v>
+        <v>-17.0259812634997</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.198579999561595</v>
       </c>
       <c r="E89">
-        <v>-34.65071457287019</v>
+        <v>-39.20173132415074</v>
       </c>
       <c r="F89">
-        <v>-3.323357980132748</v>
+        <v>-3.364151761251013</v>
       </c>
       <c r="G89">
-        <v>-13.68274905284652</v>
+        <v>-17.01640716580013</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.101227149350109</v>
       </c>
       <c r="E90">
-        <v>-35.7346070908431</v>
+        <v>-39.6152760990052</v>
       </c>
       <c r="F90">
-        <v>-2.550883839469736</v>
+        <v>-3.209428469388718</v>
       </c>
       <c r="G90">
-        <v>-12.62772288184557</v>
+        <v>-17.52361253732633</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.050615904859706</v>
       </c>
       <c r="E91">
-        <v>-35.99471810936968</v>
+        <v>-40.7848292313072</v>
       </c>
       <c r="F91">
-        <v>-2.397804028534596</v>
+        <v>-3.313695902746495</v>
       </c>
       <c r="G91">
-        <v>-12.89886980369404</v>
+        <v>-16.96800367947045</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.059105761002678</v>
       </c>
       <c r="E92">
-        <v>-38.2753980023267</v>
+        <v>-41.2386004407718</v>
       </c>
       <c r="F92">
-        <v>-2.857013640113516</v>
+        <v>-3.47584053817047</v>
       </c>
       <c r="G92">
-        <v>-12.80176488193614</v>
+        <v>-17.03331577714196</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.130188207061504</v>
       </c>
       <c r="E93">
-        <v>-39.35500431965135</v>
+        <v>-42.90064776377798</v>
       </c>
       <c r="F93">
-        <v>-3.202690528934347</v>
+        <v>-3.612642101273197</v>
       </c>
       <c r="G93">
-        <v>-12.10382905025591</v>
+        <v>-17.03813924199268</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.253250438530559</v>
       </c>
       <c r="E94">
-        <v>-40.87805918994011</v>
+        <v>-44.20077491561715</v>
       </c>
       <c r="F94">
-        <v>-3.357826347763235</v>
+        <v>-3.857858733319518</v>
       </c>
       <c r="G94">
-        <v>-12.04735776444702</v>
+        <v>-17.22710021555597</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.434458087323881</v>
       </c>
       <c r="E95">
-        <v>-41.68261958146088</v>
+        <v>-45.26474894066731</v>
       </c>
       <c r="F95">
-        <v>-3.338554380137105</v>
+        <v>-3.8983617574794</v>
       </c>
       <c r="G95">
-        <v>-12.46128520485872</v>
+        <v>-17.36552736673505</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.680075419516433</v>
       </c>
       <c r="E96">
-        <v>-42.78257006826498</v>
+        <v>-46.58117180622308</v>
       </c>
       <c r="F96">
-        <v>-4.265873582670623</v>
+        <v>-4.143882400362548</v>
       </c>
       <c r="G96">
-        <v>-12.16144578482139</v>
+        <v>-17.51754596262561</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.979704269408916</v>
       </c>
       <c r="E97">
-        <v>-44.51861718503051</v>
+        <v>-47.61788215351007</v>
       </c>
       <c r="F97">
-        <v>-4.268057987511805</v>
+        <v>-4.113053879099962</v>
       </c>
       <c r="G97">
-        <v>-11.52405320996335</v>
+        <v>-17.68911001938003</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.32515130439328</v>
       </c>
       <c r="E98">
-        <v>-46.80472218984873</v>
+        <v>-49.51060314975597</v>
       </c>
       <c r="F98">
-        <v>-4.864697064684774</v>
+        <v>-4.166406538412069</v>
       </c>
       <c r="G98">
-        <v>-12.45985835973129</v>
+        <v>-17.82719287382304</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.70241466444551</v>
       </c>
       <c r="E99">
-        <v>-49.22666443311953</v>
+        <v>-50.94751285899681</v>
       </c>
       <c r="F99">
-        <v>-4.30599638619262</v>
+        <v>-4.265003796897683</v>
       </c>
       <c r="G99">
-        <v>-13.07423602200032</v>
+        <v>-17.74431998733846</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.12808855960849</v>
       </c>
       <c r="E100">
-        <v>-50.23784890454378</v>
+        <v>-52.16551726682538</v>
       </c>
       <c r="F100">
-        <v>-5.450341221320385</v>
+        <v>-4.419085104022808</v>
       </c>
       <c r="G100">
-        <v>-12.52677441671658</v>
+        <v>-18.01531296881935</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.55224478490082</v>
       </c>
       <c r="E101">
-        <v>-51.93155252510059</v>
+        <v>-53.74986163645245</v>
       </c>
       <c r="F101">
-        <v>-4.698746081044935</v>
+        <v>-4.631365019766418</v>
       </c>
       <c r="G101">
-        <v>-13.73216887665676</v>
+        <v>-17.71523187895766</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.01442230487621</v>
       </c>
       <c r="E102">
-        <v>-52.38082356352006</v>
+        <v>-55.26885333343782</v>
       </c>
       <c r="F102">
-        <v>-5.614320690541561</v>
+        <v>-4.700101290115915</v>
       </c>
       <c r="G102">
-        <v>-14.366585271075</v>
+        <v>-18.2347657220721</v>
       </c>
     </row>
   </sheetData>
